--- a/artfynd/S 1273-2023 artfynd.xlsx
+++ b/artfynd/S 1273-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/148081</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/166567</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/169992</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065272</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1238,6 +1263,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065286</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1352,6 +1382,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065289</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1468,6 +1503,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/158170</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1583,6 +1623,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/191079</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1694,6 +1739,11 @@
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/174814</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1796,6 +1846,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/179205</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1907,6 +1962,11 @@
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/298550</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2017,6 +2077,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/443639</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2137,6 +2202,11 @@
           <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/443933</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2257,6 +2327,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/445273</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2377,6 +2452,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/445573</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2497,6 +2577,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6806913</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2616,6 +2701,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71934892</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2715,6 +2805,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101686777</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2821,6 +2916,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/627439</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2918,6 +3018,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065306</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3015,6 +3120,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065363</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3132,6 +3242,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14647306</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3238,6 +3353,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66240230</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3344,6 +3464,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66240233</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3460,6 +3585,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3001538</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3566,6 +3696,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66240234</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3667,6 +3802,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065376</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3773,6 +3913,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66240229</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3879,6 +4024,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78048116</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3993,6 +4143,11 @@
       <c r="AY31" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3708535</t>
         </is>
       </c>
     </row>
@@ -4114,6 +4269,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66420053</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4225,6 +4385,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4808317</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4331,6 +4496,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4817457</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4437,6 +4607,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66240235</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4538,6 +4713,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065250</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4639,6 +4819,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065257</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4743,6 +4928,11 @@
       <c r="AY38" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5791388</t>
         </is>
       </c>
     </row>
@@ -4852,6 +5042,11 @@
       <c r="AY39" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66419945</t>
         </is>
       </c>
     </row>
@@ -4959,8 +5154,54 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66419950</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>